--- a/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7140"/>
+    <workbookView windowWidth="27950" windowHeight="12550"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,6 +107,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">序号
 </t>
     </r>
@@ -123,6 +130,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">机台
 </t>
     </r>
@@ -139,6 +153,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">结构
 </t>
     </r>
@@ -185,6 +206,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">余量
 </t>
     </r>
@@ -201,6 +229,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">收尾时间（4天以内）
 </t>
     </r>
@@ -210,7 +245,6 @@
         <sz val="9"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <charset val="0"/>
       </rPr>
       <t>THỜI GIAN KẾT THÚC (Báo trước 4 ngày)</t>
@@ -233,6 +267,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">预计
 </t>
     </r>
@@ -242,7 +283,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <charset val="0"/>
       </rPr>
       <t>DỰ KIẾN</t>
@@ -250,6 +290,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Microsoft YaHei"/>
+        <charset val="0"/>
+      </rPr>
       <t xml:space="preserve">月计划
 </t>
     </r>
@@ -259,7 +306,6 @@
         <sz val="9"/>
         <color indexed="9"/>
         <rFont val="Arial"/>
-        <family val="2"/>
         <charset val="0"/>
       </rPr>
       <t>KH THÁNG</t>
@@ -293,31 +339,31 @@
     <t>{.stt}</t>
   </si>
   <si>
-    <t>{.cxMachineCode}</t>
-  </si>
-  <si>
-    <t>{.materialSpec}</t>
-  </si>
-  <si>
-    <t>{.qty}</t>
-  </si>
-  <si>
-    <t>{.receivePlanDate}</t>
-  </si>
-  <si>
-    <t>{.receiveChangeDate}</t>
+    <t>{.machineCode}</t>
+  </si>
+  <si>
+    <t>{.structureSpec}</t>
+  </si>
+  <si>
+    <t>{.remainQty}</t>
+  </si>
+  <si>
+    <t>{.receiveEstDate}</t>
+  </si>
+  <si>
+    <t>{.receiveMonthPlan}</t>
   </si>
   <si>
     <t>{.remark}</t>
   </si>
   <si>
-    <t>{.orderNo}</t>
-  </si>
-  <si>
-    <t>{.vulcanizePlanDate}</t>
-  </si>
-  <si>
-    <t>{.vulcanizeChangeDate}</t>
+    <t>{.nextStructure}</t>
+  </si>
+  <si>
+    <t>{.startEstDate}</t>
+  </si>
+  <si>
+    <t>{.startMonthPlan}</t>
   </si>
   <si>
     <t>{.remark2}</t>
@@ -357,7 +403,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,8 +441,12 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="0"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -554,15 +604,6 @@
       <sz val="9"/>
       <color indexed="9"/>
       <name val="Arial"/>
-      <family val="2"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
@@ -580,12 +621,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="0"/>
@@ -1002,137 +1050,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1173,10 +1221,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1663,7 +1708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="28" spans="1:19">
+    <row r="3" ht="23" spans="1:19">
       <c r="A3" s="14" t="s">
         <v>19</v>
       </c>
@@ -1712,13 +1757,13 @@
       <c r="P3" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="Q3" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="R3" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="15" t="s">
+      <c r="S3" s="14" t="s">
         <v>37</v>
       </c>
     </row>

--- a/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27950" windowHeight="12550"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="成型结构切换" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,290 +26,209 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Admin</author>
-  </authors>
-  <commentList>
-    <comment ref="G1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-备注栏可以编辑</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-备注栏可以编辑</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t>Admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="Tahoma"/>
-            <charset val="0"/>
-          </rPr>
-          <t xml:space="preserve">
-如果备料了，写OK
-如果还没备，写班次备料。比如：05.09日中班</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
-    <r>
-      <rPr>
-        <b/>
+    <t>序号
+STT</t>
+  </si>
+  <si>
+    <t>机台
+MÁY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">序号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+      <t>结构
+QUY CÁCH TR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Cambria"/>
         <charset val="134"/>
       </rPr>
-      <t>STT</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>ƯỚ</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">机台
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MÁY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>C</t>
+    </r>
+  </si>
+  <si>
+    <t>余量
+SỐ LƯỢNG CÒN THIẾU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">结构
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+      <t>收尾时间（4天以内）
+THỜI GIAN KẾT THÚC (Báo tr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>QUY CÁCH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> TR</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ƯỚ</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
+      <t>ớc 4 ngày)</t>
+    </r>
+  </si>
+  <si>
+    <t>备注
+GHI CHÚ</t>
+  </si>
+  <si>
+    <t>后结构
+QUY CÁCH SAU</t>
+  </si>
+  <si>
+    <t>开产时间
+THỜI GIAN BẮT ĐẦU</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>C</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>备料进度Ti</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ế</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <color theme="0"/>
         <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">余量
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
+      <t xml:space="preserve">n </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Segoe UI"/>
+        <charset val="238"/>
+      </rPr>
+      <t>đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
         <charset val="134"/>
       </rPr>
-      <t>SỐ LƯỢNG CÒN THIẾU</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">收尾时间（4天以内）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>THỜI GIAN KẾT THÚC (Báo trước 4 ngày)</t>
-    </r>
-  </si>
-  <si>
-    <t>备注
-GHI CHÚ</t>
-  </si>
-  <si>
-    <t>后结构
-QUY CÁCH SAU</t>
-  </si>
-  <si>
-    <t>开产时间
-THỜI GIAN BẮT ĐẦU</t>
-  </si>
-  <si>
-    <t>备料进度</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">预计
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color indexed="9"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>DỰ KIẾN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color theme="0"/>
-        <rFont val="Microsoft YaHei"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve">月计划
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color indexed="9"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>KH THÁNG</t>
-    </r>
+      <t xml:space="preserve"> chu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ẩ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>n b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Calibri"/>
+        <charset val="163"/>
+      </rPr>
+      <t>ệ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>u</t>
+    </r>
+  </si>
+  <si>
+    <t>预计
+DỰ KIẾN</t>
+  </si>
+  <si>
+    <t>月计划
+KH THÁNG</t>
   </si>
   <si>
     <t>TD</t>
@@ -403,7 +322,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -412,231 +331,189 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color theme="0"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="0"/>
       <name val="Microsoft YaHei"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="9"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1050,178 +927,164 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1608,162 +1471,150 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="8.52727272727273" defaultRowHeight="17.5" outlineLevelRow="2"/>
-  <cols>
-    <col min="1" max="1" width="5.45454545454545" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.48181818181818" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.8636363636364" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.7727272727273" style="5" customWidth="1"/>
-    <col min="5" max="6" width="15.6181818181818" style="5" customWidth="1"/>
-    <col min="7" max="7" width="16.1636363636364" style="5" customWidth="1"/>
-    <col min="8" max="8" width="26.8636363636364" style="4" customWidth="1"/>
-    <col min="9" max="10" width="15.6181818181818" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16.1636363636364" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.52727272727273" style="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="38.45" customHeight="1" spans="1:19">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:19">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8"/>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="4"/>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="27" customHeight="1" spans="1:19">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13" t="s">
+    <row r="2" ht="23" spans="1:19">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13" t="s">
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="6" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="S2" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" ht="23" spans="1:19">
-      <c r="A3" s="14" t="s">
+    <row r="3" s="1" customFormat="1" ht="23" spans="1:19">
+      <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="14" t="s">
+      <c r="L3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="14" t="s">
+      <c r="M3" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="14" t="s">
+      <c r="O3" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="Q3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="14" t="s">
+      <c r="R3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="14" t="s">
+      <c r="S3" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1780,9 +1631,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="K1:K2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
+++ b/APS-Modules/aps-cx/src/main/resources/excelModel/cxStructureChangeExportTemp.xlsx
@@ -506,13 +506,13 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Cambria"/>
+      <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="Microsoft YaHei"/>
+      <name val="Cambria"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1057,7 +1057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1086,6 +1086,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1559,14 +1562,14 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="23" spans="1:19">
+    <row r="3" s="1" customFormat="1" ht="17.55" customHeight="1" spans="1:19">
       <c r="A3" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -1581,7 +1584,7 @@
       <c r="G3" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I3" s="10" t="s">
